--- a/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
+++ b/docs/UNIVERSAL_TAG_MASTER_BUILD.xlsx
@@ -601,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2489,17 +2489,17 @@
       </c>
       <c r="C42" s="24" t="inlineStr">
         <is>
-          <t>Show T7 - Installation - ASS_INSTALL_DATE_TXT</t>
+          <t>Show T7 - Fabrication - Spool No</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_7_BOOL, ASS_INSTALL_DATE_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_7_BOOL, ASS_SPOOL_NR_TXT, "")</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
         <is>
-          <t>Installed:</t>
+          <t>Spool:</t>
         </is>
       </c>
       <c r="F42" s="22" t="inlineStr"/>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J42" s="22" t="inlineStr">
         <is>
-          <t>ASS_INSTALL_DATE_TXT</t>
+          <t>ASS_SPOOL_NR_TXT</t>
         </is>
       </c>
       <c r="K42" s="22" t="inlineStr"/>
@@ -2534,24 +2534,20 @@
       </c>
       <c r="C43" s="24" t="inlineStr">
         <is>
-          <t>Show T7 - Installation - CST_INSTALL_HRS_DISP_TXT</t>
+          <t>Show T7 - Fabrication - Status</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_7_BOOL, CST_INSTALL_HRS_DISP_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_7_BOOL, ASS_FAB_STATUS_TXT, "")</t>
         </is>
       </c>
       <c r="E43" s="22" t="inlineStr">
         <is>
-          <t>Hrs:</t>
-        </is>
-      </c>
-      <c r="F43" s="22" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
+          <t>Fab:</t>
+        </is>
+      </c>
+      <c r="F43" s="22" t="inlineStr"/>
       <c r="G43" s="22" t="n">
         <v>0</v>
       </c>
@@ -2567,7 +2563,7 @@
       </c>
       <c r="J43" s="22" t="inlineStr">
         <is>
-          <t>CST_INSTALL_HRS_DISP_TXT</t>
+          <t>ASS_FAB_STATUS_TXT</t>
         </is>
       </c>
       <c r="K43" s="22" t="inlineStr"/>
@@ -2583,178 +2579,182 @@
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
+          <t>Show T7 - QC - Inspector</t>
+        </is>
+      </c>
+      <c r="D44" s="25" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_7_BOOL, ASS_QC_INSPECTOR_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="inlineStr">
+        <is>
+          <t>QC:</t>
+        </is>
+      </c>
+      <c r="F44" s="22" t="inlineStr"/>
+      <c r="G44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="22" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I44" s="22" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_7_BOOL</t>
+        </is>
+      </c>
+      <c r="J44" s="22" t="inlineStr">
+        <is>
+          <t>ASS_QC_INSPECTOR_TXT</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>Show T7 - Installation - ASS_INSTALL_DATE_TXT</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_7_BOOL, ASS_INSTALL_DATE_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="inlineStr">
+        <is>
+          <t>Installed:</t>
+        </is>
+      </c>
+      <c r="F45" s="22" t="inlineStr"/>
+      <c r="G45" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I45" s="22" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_7_BOOL</t>
+        </is>
+      </c>
+      <c r="J45" s="22" t="inlineStr">
+        <is>
+          <t>ASS_INSTALL_DATE_TXT</t>
+        </is>
+      </c>
+      <c r="K45" s="22" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Show T7 - Installation - CST_INSTALL_HRS_DISP_TXT</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_7_BOOL, CST_INSTALL_HRS_DISP_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="inlineStr">
+        <is>
+          <t>Hrs:</t>
+        </is>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I46" s="22" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_7_BOOL</t>
+        </is>
+      </c>
+      <c r="J46" s="22" t="inlineStr">
+        <is>
+          <t>CST_INSTALL_HRS_DISP_TXT</t>
+        </is>
+      </c>
+      <c r="K46" s="22" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
           <t>Show T7 - Installation - ASS_CST_INSTALL_UGX_NR</t>
         </is>
       </c>
-      <c r="D44" s="25" t="inlineStr">
+      <c r="D47" s="25" t="inlineStr">
         <is>
           <t>if(TAG_PARA_STATE_7_BOOL, ASS_CST_INSTALL_UGX_NR, "")</t>
         </is>
       </c>
-      <c r="E44" s="22" t="inlineStr">
+      <c r="E47" s="22" t="inlineStr">
         <is>
           <t>@</t>
         </is>
       </c>
-      <c r="F44" s="22" t="inlineStr">
+      <c r="F47" s="22" t="inlineStr">
         <is>
           <t>UGX</t>
         </is>
       </c>
-      <c r="G44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="22" t="inlineStr">
+      <c r="G47" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I44" s="22" t="inlineStr">
+      <c r="I47" s="22" t="inlineStr">
         <is>
           <t>TAG_PARA_STATE_7_BOOL</t>
         </is>
       </c>
-      <c r="J44" s="22" t="inlineStr">
+      <c r="J47" s="22" t="inlineStr">
         <is>
           <t>ASS_CST_INSTALL_UGX_NR</t>
         </is>
       </c>
-      <c r="K44" s="22" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="27" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="C45" s="28" t="inlineStr">
-        <is>
-          <t>Show T8 - Clash - Triage Severity</t>
-        </is>
-      </c>
-      <c r="D45" s="29" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_TRIAGE_SEVERITY_NR_DISP_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E45" s="26" t="inlineStr">
-        <is>
-          <t>Sev:</t>
-        </is>
-      </c>
-      <c r="F45" s="26" t="inlineStr">
-        <is>
-          <t>/5</t>
-        </is>
-      </c>
-      <c r="G45" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I45" s="26" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_8_BOOL</t>
-        </is>
-      </c>
-      <c r="J45" s="26" t="inlineStr">
-        <is>
-          <t>CLASH_TRIAGE_SEVERITY_NR_DISP_TXT</t>
-        </is>
-      </c>
-      <c r="K45" s="26" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="27" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="C46" s="28" t="inlineStr">
-        <is>
-          <t>Show T8 - Clash - Triage Category</t>
-        </is>
-      </c>
-      <c r="D46" s="29" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_TRIAGE_CATEGORY_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr"/>
-      <c r="F46" s="26" t="inlineStr"/>
-      <c r="G46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_8_BOOL</t>
-        </is>
-      </c>
-      <c r="J46" s="26" t="inlineStr">
-        <is>
-          <t>CLASH_TRIAGE_CATEGORY_TXT</t>
-        </is>
-      </c>
-      <c r="K46" s="26" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="26" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="27" t="inlineStr">
-        <is>
-          <t>T8</t>
-        </is>
-      </c>
-      <c r="C47" s="28" t="inlineStr">
-        <is>
-          <t>Show T8 - Clash - Resolution Status</t>
-        </is>
-      </c>
-      <c r="D47" s="29" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_RESOLUTION_STATUS_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E47" s="26" t="inlineStr">
-        <is>
-          <t>Res:</t>
-        </is>
-      </c>
-      <c r="F47" s="26" t="inlineStr"/>
-      <c r="G47" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="26" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I47" s="26" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_8_BOOL</t>
-        </is>
-      </c>
-      <c r="J47" s="26" t="inlineStr">
-        <is>
-          <t>CLASH_RESOLUTION_STATUS_TXT</t>
-        </is>
-      </c>
-      <c r="K47" s="26" t="inlineStr"/>
+      <c r="K47" s="22" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="26" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>Show T8 - Coordination - ASS_CRITICALITY_RATING_NR</t>
+          <t>Show T8 - Clash - Triage Severity</t>
         </is>
       </c>
       <c r="D48" s="29" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, ASS_CRITICALITY_RATING_NR, "")</t>
+          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_TRIAGE_SEVERITY_NR_DISP_TXT, "")</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>Crit:</t>
+          <t>Sev:</t>
         </is>
       </c>
       <c r="F48" s="26" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J48" s="26" t="inlineStr">
         <is>
-          <t>ASS_CRITICALITY_RATING_NR</t>
+          <t>CLASH_TRIAGE_SEVERITY_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="K48" s="26" t="inlineStr"/>
@@ -2816,19 +2816,15 @@
       </c>
       <c r="C49" s="28" t="inlineStr">
         <is>
-          <t>Show T8 - Coordination - ASS_ZONE_TXT</t>
+          <t>Show T8 - Clash - Triage Category</t>
         </is>
       </c>
       <c r="D49" s="29" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, ASS_ZONE_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E49" s="26" t="inlineStr">
-        <is>
-          <t>Zone:</t>
-        </is>
-      </c>
+          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_TRIAGE_CATEGORY_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E49" s="26" t="inlineStr"/>
       <c r="F49" s="26" t="inlineStr"/>
       <c r="G49" s="26" t="n">
         <v>0</v>
@@ -2845,7 +2841,7 @@
       </c>
       <c r="J49" s="26" t="inlineStr">
         <is>
-          <t>ASS_ZONE_TXT</t>
+          <t>CLASH_TRIAGE_CATEGORY_TXT</t>
         </is>
       </c>
       <c r="K49" s="26" t="inlineStr"/>
@@ -2861,17 +2857,17 @@
       </c>
       <c r="C50" s="28" t="inlineStr">
         <is>
-          <t>Show T8 - Coordination - ASS_LVL_COD_TXT</t>
+          <t>Show T8 - Clash - Resolution Status</t>
         </is>
       </c>
       <c r="D50" s="29" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_8_BOOL, ASS_LVL_COD_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_8_BOOL, CLASH_RESOLUTION_STATUS_TXT, "")</t>
         </is>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
-          <t>Lvl:</t>
+          <t>Res:</t>
         </is>
       </c>
       <c r="F50" s="26" t="inlineStr"/>
@@ -2890,153 +2886,149 @@
       </c>
       <c r="J50" s="26" t="inlineStr">
         <is>
+          <t>CLASH_RESOLUTION_STATUS_TXT</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C51" s="28" t="inlineStr">
+        <is>
+          <t>Show T8 - Coordination - ASS_CRITICALITY_RATING_NR</t>
+        </is>
+      </c>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_8_BOOL, ASS_CRITICALITY_RATING_NR, "")</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="inlineStr">
+        <is>
+          <t>Crit:</t>
+        </is>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>/5</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I51" s="26" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_8_BOOL</t>
+        </is>
+      </c>
+      <c r="J51" s="26" t="inlineStr">
+        <is>
+          <t>ASS_CRITICALITY_RATING_NR</t>
+        </is>
+      </c>
+      <c r="K51" s="26" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C52" s="28" t="inlineStr">
+        <is>
+          <t>Show T8 - Coordination - ASS_ZONE_TXT</t>
+        </is>
+      </c>
+      <c r="D52" s="29" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_8_BOOL, ASS_ZONE_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E52" s="26" t="inlineStr">
+        <is>
+          <t>Zone:</t>
+        </is>
+      </c>
+      <c r="F52" s="26" t="inlineStr"/>
+      <c r="G52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I52" s="26" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_8_BOOL</t>
+        </is>
+      </c>
+      <c r="J52" s="26" t="inlineStr">
+        <is>
+          <t>ASS_ZONE_TXT</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>Show T8 - Coordination - ASS_LVL_COD_TXT</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_8_BOOL, ASS_LVL_COD_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E53" s="26" t="inlineStr">
+        <is>
+          <t>Lvl:</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr"/>
+      <c r="G53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I53" s="26" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_8_BOOL</t>
+        </is>
+      </c>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
           <t>ASS_LVL_COD_TXT</t>
         </is>
       </c>
-      <c r="K50" s="26" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="31" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>Show T9 - As-built - Deviation</t>
-        </is>
-      </c>
-      <c r="D51" s="33" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_9_BOOL, ASBUILT_DEVIATION_MM_DISP_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E51" s="30" t="inlineStr">
-        <is>
-          <t>Δ:</t>
-        </is>
-      </c>
-      <c r="F51" s="30" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="G51" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I51" s="30" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_9_BOOL</t>
-        </is>
-      </c>
-      <c r="J51" s="30" t="inlineStr">
-        <is>
-          <t>ASBUILT_DEVIATION_MM_DISP_TXT</t>
-        </is>
-      </c>
-      <c r="K51" s="30" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="30" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="31" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>Show T9 - As-built - Capture Date</t>
-        </is>
-      </c>
-      <c r="D52" s="33" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_9_BOOL, ASBUILT_CAPTURE_DATE_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E52" s="30" t="inlineStr">
-        <is>
-          <t>on</t>
-        </is>
-      </c>
-      <c r="F52" s="30" t="inlineStr"/>
-      <c r="G52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I52" s="30" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_9_BOOL</t>
-        </is>
-      </c>
-      <c r="J52" s="30" t="inlineStr">
-        <is>
-          <t>ASBUILT_CAPTURE_DATE_TXT</t>
-        </is>
-      </c>
-      <c r="K52" s="30" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="30" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>T9</t>
-        </is>
-      </c>
-      <c r="C53" s="32" t="inlineStr">
-        <is>
-          <t>Show T9 - Health Score</t>
-        </is>
-      </c>
-      <c r="D53" s="33" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_9_BOOL, HEALTH_SCORE_LAST_NR_DISP_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E53" s="30" t="inlineStr">
-        <is>
-          <t>Health:</t>
-        </is>
-      </c>
-      <c r="F53" s="30" t="inlineStr">
-        <is>
-          <t>/100</t>
-        </is>
-      </c>
-      <c r="G53" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="30" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I53" s="30" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_9_BOOL</t>
-        </is>
-      </c>
-      <c r="J53" s="30" t="inlineStr">
-        <is>
-          <t>HEALTH_SCORE_LAST_NR_DISP_TXT</t>
-        </is>
-      </c>
-      <c r="K53" s="30" t="inlineStr"/>
+      <c r="K53" s="26" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="30" t="n">
@@ -3049,20 +3041,24 @@
       </c>
       <c r="C54" s="32" t="inlineStr">
         <is>
-          <t>Show T9 - Warranty &amp; quality - ASS_WARRANTY_PARTS_TXT</t>
+          <t>Show T9 - As-built - Deviation</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_9_BOOL, ASS_WARRANTY_PARTS_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_9_BOOL, ASBUILT_DEVIATION_MM_DISP_TXT, "")</t>
         </is>
       </c>
       <c r="E54" s="30" t="inlineStr">
         <is>
-          <t>Parts:</t>
-        </is>
-      </c>
-      <c r="F54" s="30" t="inlineStr"/>
+          <t>Δ:</t>
+        </is>
+      </c>
+      <c r="F54" s="30" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="G54" s="30" t="n">
         <v>0</v>
       </c>
@@ -3078,7 +3074,7 @@
       </c>
       <c r="J54" s="30" t="inlineStr">
         <is>
-          <t>ASS_WARRANTY_PARTS_TXT</t>
+          <t>ASBUILT_DEVIATION_MM_DISP_TXT</t>
         </is>
       </c>
       <c r="K54" s="30" t="inlineStr"/>
@@ -3094,17 +3090,17 @@
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
-          <t>Show T9 - Warranty &amp; quality - ASS_WARRANTY_LABOR_TXT</t>
+          <t>Show T9 - As-built - Capture Date</t>
         </is>
       </c>
       <c r="D55" s="33" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_9_BOOL, ASS_WARRANTY_LABOR_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_9_BOOL, ASBUILT_CAPTURE_DATE_TXT, "")</t>
         </is>
       </c>
       <c r="E55" s="30" t="inlineStr">
         <is>
-          <t>Labor:</t>
+          <t>on</t>
         </is>
       </c>
       <c r="F55" s="30" t="inlineStr"/>
@@ -3123,7 +3119,7 @@
       </c>
       <c r="J55" s="30" t="inlineStr">
         <is>
-          <t>ASS_WARRANTY_LABOR_TXT</t>
+          <t>ASBUILT_CAPTURE_DATE_TXT</t>
         </is>
       </c>
       <c r="K55" s="30" t="inlineStr"/>
@@ -3139,174 +3135,178 @@
       </c>
       <c r="C56" s="32" t="inlineStr">
         <is>
+          <t>Show T9 - Health Score</t>
+        </is>
+      </c>
+      <c r="D56" s="33" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_9_BOOL, HEALTH_SCORE_LAST_NR_DISP_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>Health:</t>
+        </is>
+      </c>
+      <c r="F56" s="30" t="inlineStr">
+        <is>
+          <t>/100</t>
+        </is>
+      </c>
+      <c r="G56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_9_BOOL</t>
+        </is>
+      </c>
+      <c r="J56" s="30" t="inlineStr">
+        <is>
+          <t>HEALTH_SCORE_LAST_NR_DISP_TXT</t>
+        </is>
+      </c>
+      <c r="K56" s="30" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="30" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>Show T9 - Warranty &amp; quality - ASS_WARRANTY_PARTS_TXT</t>
+        </is>
+      </c>
+      <c r="D57" s="33" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_9_BOOL, ASS_WARRANTY_PARTS_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E57" s="30" t="inlineStr">
+        <is>
+          <t>Parts:</t>
+        </is>
+      </c>
+      <c r="F57" s="30" t="inlineStr"/>
+      <c r="G57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I57" s="30" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_9_BOOL</t>
+        </is>
+      </c>
+      <c r="J57" s="30" t="inlineStr">
+        <is>
+          <t>ASS_WARRANTY_PARTS_TXT</t>
+        </is>
+      </c>
+      <c r="K57" s="30" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="30" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Show T9 - Warranty &amp; quality - ASS_WARRANTY_LABOR_TXT</t>
+        </is>
+      </c>
+      <c r="D58" s="33" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_9_BOOL, ASS_WARRANTY_LABOR_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>Labor:</t>
+        </is>
+      </c>
+      <c r="F58" s="30" t="inlineStr"/>
+      <c r="G58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I58" s="30" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_9_BOOL</t>
+        </is>
+      </c>
+      <c r="J58" s="30" t="inlineStr">
+        <is>
+          <t>ASS_WARRANTY_LABOR_TXT</t>
+        </is>
+      </c>
+      <c r="K58" s="30" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
           <t>Show T9 - Warranty &amp; quality - ASS_WARRANTY_TXT</t>
         </is>
       </c>
-      <c r="D56" s="33" t="inlineStr">
+      <c r="D59" s="33" t="inlineStr">
         <is>
           <t>if(TAG_PARA_STATE_9_BOOL, ASS_WARRANTY_TXT, "")</t>
         </is>
       </c>
-      <c r="E56" s="30" t="inlineStr">
+      <c r="E59" s="30" t="inlineStr">
         <is>
           <t>Terms:</t>
         </is>
       </c>
-      <c r="F56" s="30" t="inlineStr"/>
-      <c r="G56" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="30" t="inlineStr">
+      <c r="F59" s="30" t="inlineStr"/>
+      <c r="G59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="30" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I56" s="30" t="inlineStr">
+      <c r="I59" s="30" t="inlineStr">
         <is>
           <t>TAG_PARA_STATE_9_BOOL</t>
         </is>
       </c>
-      <c r="J56" s="30" t="inlineStr">
+      <c r="J59" s="30" t="inlineStr">
         <is>
           <t>ASS_WARRANTY_TXT</t>
         </is>
       </c>
-      <c r="K56" s="30" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="35" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="C57" s="36" t="inlineStr">
-        <is>
-          <t>Show T10 - Compliance - IFC PSet Override</t>
-        </is>
-      </c>
-      <c r="D57" s="37" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, IFC_PSET_OVERRIDE_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E57" s="34" t="inlineStr">
-        <is>
-          <t>IFC:</t>
-        </is>
-      </c>
-      <c r="F57" s="34" t="inlineStr"/>
-      <c r="G57" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I57" s="34" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_10_BOOL</t>
-        </is>
-      </c>
-      <c r="J57" s="34" t="inlineStr">
-        <is>
-          <t>IFC_PSET_OVERRIDE_TXT</t>
-        </is>
-      </c>
-      <c r="K57" s="34" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="C58" s="36" t="inlineStr">
-        <is>
-          <t>Show T10 - Compliance - ACC Issue</t>
-        </is>
-      </c>
-      <c r="D58" s="37" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ACC_ISSUE_ID_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E58" s="34" t="inlineStr">
-        <is>
-          <t>ACC:</t>
-        </is>
-      </c>
-      <c r="F58" s="34" t="inlineStr"/>
-      <c r="G58" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I58" s="34" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_10_BOOL</t>
-        </is>
-      </c>
-      <c r="J58" s="34" t="inlineStr">
-        <is>
-          <t>ACC_ISSUE_ID_TXT</t>
-        </is>
-      </c>
-      <c r="K58" s="34" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="34" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="35" t="inlineStr">
-        <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="inlineStr">
-        <is>
-          <t>Show T10 - Compliance - ACC Sync Status</t>
-        </is>
-      </c>
-      <c r="D59" s="37" t="inlineStr">
-        <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ACC_SYNC_STATUS_TXT, "")</t>
-        </is>
-      </c>
-      <c r="E59" s="34" t="inlineStr">
-        <is>
-          <t>Sync:</t>
-        </is>
-      </c>
-      <c r="F59" s="34" t="inlineStr"/>
-      <c r="G59" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="34" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="I59" s="34" t="inlineStr">
-        <is>
-          <t>TAG_PARA_STATE_10_BOOL</t>
-        </is>
-      </c>
-      <c r="J59" s="34" t="inlineStr">
-        <is>
-          <t>ACC_SYNC_STATUS_TXT</t>
-        </is>
-      </c>
-      <c r="K59" s="34" t="inlineStr"/>
+      <c r="K59" s="30" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="34" t="n">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="C60" s="36" t="inlineStr">
         <is>
-          <t>Show T10 - Classification - ASS_UNICLASS_2015_TXT</t>
+          <t>Show T10 - Compliance - IFC PSet Override</t>
         </is>
       </c>
       <c r="D60" s="37" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ASS_UNICLASS_2015_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_10_BOOL, IFC_PSET_OVERRIDE_TXT, "")</t>
         </is>
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>Uniclass:</t>
+          <t>IFC:</t>
         </is>
       </c>
       <c r="F60" s="34" t="inlineStr"/>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="J60" s="34" t="inlineStr">
         <is>
-          <t>ASS_UNICLASS_2015_TXT</t>
+          <t>IFC_PSET_OVERRIDE_TXT</t>
         </is>
       </c>
       <c r="K60" s="34" t="inlineStr"/>
@@ -3364,17 +3364,17 @@
       </c>
       <c r="C61" s="36" t="inlineStr">
         <is>
-          <t>Show T10 - Classification - ASS_KEYNOTE_TXT</t>
+          <t>Show T10 - Compliance - ACC Issue</t>
         </is>
       </c>
       <c r="D61" s="37" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ASS_KEYNOTE_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_10_BOOL, ACC_ISSUE_ID_TXT, "")</t>
         </is>
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>Key:</t>
+          <t>ACC:</t>
         </is>
       </c>
       <c r="F61" s="34" t="inlineStr"/>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="J61" s="34" t="inlineStr">
         <is>
-          <t>ASS_KEYNOTE_TXT</t>
+          <t>ACC_ISSUE_ID_TXT</t>
         </is>
       </c>
       <c r="K61" s="34" t="inlineStr"/>
@@ -3409,17 +3409,17 @@
       </c>
       <c r="C62" s="36" t="inlineStr">
         <is>
-          <t>Show T10 - Classification - ASS_MODEL_REF_TXT</t>
+          <t>Show T10 - Compliance - ACC Sync Status</t>
         </is>
       </c>
       <c r="D62" s="37" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ASS_MODEL_REF_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_10_BOOL, ACC_SYNC_STATUS_TXT, "")</t>
         </is>
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>Ref:</t>
+          <t>Sync:</t>
         </is>
       </c>
       <c r="F62" s="34" t="inlineStr"/>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="J62" s="34" t="inlineStr">
         <is>
-          <t>ASS_MODEL_REF_TXT</t>
+          <t>ACC_SYNC_STATUS_TXT</t>
         </is>
       </c>
       <c r="K62" s="34" t="inlineStr"/>
@@ -3454,17 +3454,17 @@
       </c>
       <c r="C63" s="36" t="inlineStr">
         <is>
-          <t>Show T10-Ph179 - Trace Seq</t>
+          <t>Show T10 - Classification - ASS_UNICLASS_2015_TXT</t>
         </is>
       </c>
       <c r="D63" s="37" t="inlineStr">
         <is>
-          <t>if(TAG_PARA_STATE_10_BOOL, ASS_TRACE_SEQ_NR_DISP_TXT, "")</t>
+          <t>if(TAG_PARA_STATE_10_BOOL, ASS_UNICLASS_2015_TXT, "")</t>
         </is>
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>Trc:</t>
+          <t>Uniclass:</t>
         </is>
       </c>
       <c r="F63" s="34" t="inlineStr"/>
@@ -3473,20 +3473,155 @@
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I63" s="34" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_10_BOOL</t>
+        </is>
+      </c>
+      <c r="J63" s="34" t="inlineStr">
+        <is>
+          <t>ASS_UNICLASS_2015_TXT</t>
+        </is>
+      </c>
+      <c r="K63" s="34" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="34" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="35" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C64" s="36" t="inlineStr">
+        <is>
+          <t>Show T10 - Classification - ASS_KEYNOTE_TXT</t>
+        </is>
+      </c>
+      <c r="D64" s="37" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_10_BOOL, ASS_KEYNOTE_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E64" s="34" t="inlineStr">
+        <is>
+          <t>Key:</t>
+        </is>
+      </c>
+      <c r="F64" s="34" t="inlineStr"/>
+      <c r="G64" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I64" s="34" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_10_BOOL</t>
+        </is>
+      </c>
+      <c r="J64" s="34" t="inlineStr">
+        <is>
+          <t>ASS_KEYNOTE_TXT</t>
+        </is>
+      </c>
+      <c r="K64" s="34" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="35" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C65" s="36" t="inlineStr">
+        <is>
+          <t>Show T10 - Classification - ASS_MODEL_REF_TXT</t>
+        </is>
+      </c>
+      <c r="D65" s="37" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_10_BOOL, ASS_MODEL_REF_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E65" s="34" t="inlineStr">
+        <is>
+          <t>Ref:</t>
+        </is>
+      </c>
+      <c r="F65" s="34" t="inlineStr"/>
+      <c r="G65" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="I63" s="34" t="inlineStr">
+      <c r="I65" s="34" t="inlineStr">
         <is>
           <t>TAG_PARA_STATE_10_BOOL</t>
         </is>
       </c>
-      <c r="J63" s="34" t="inlineStr">
+      <c r="J65" s="34" t="inlineStr">
+        <is>
+          <t>ASS_MODEL_REF_TXT</t>
+        </is>
+      </c>
+      <c r="K65" s="34" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="35" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="C66" s="36" t="inlineStr">
+        <is>
+          <t>Show T10-Ph179 - Trace Seq</t>
+        </is>
+      </c>
+      <c r="D66" s="37" t="inlineStr">
+        <is>
+          <t>if(TAG_PARA_STATE_10_BOOL, ASS_TRACE_SEQ_NR_DISP_TXT, "")</t>
+        </is>
+      </c>
+      <c r="E66" s="34" t="inlineStr">
+        <is>
+          <t>Trc:</t>
+        </is>
+      </c>
+      <c r="F66" s="34" t="inlineStr"/>
+      <c r="G66" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="I66" s="34" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_10_BOOL</t>
+        </is>
+      </c>
+      <c r="J66" s="34" t="inlineStr">
         <is>
           <t>ASS_TRACE_SEQ_NR_DISP_TXT</t>
         </is>
       </c>
-      <c r="K63" s="34" t="inlineStr"/>
+      <c r="K66" s="34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3499,7 +3634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3998,7 +4133,7 @@
     <row r="19">
       <c r="A19" s="38" t="inlineStr">
         <is>
-          <t>ASS_FLOW_RATE_TXT</t>
+          <t>ASS_FAB_STATUS_TXT</t>
         </is>
       </c>
       <c r="B19" s="38" t="inlineStr">
@@ -4008,24 +4143,24 @@
       </c>
       <c r="C19" s="38" t="inlineStr">
         <is>
-          <t>HVC_SYSTEMS</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D19" s="38" t="inlineStr">
         <is>
-          <t>d9a5078f-1c08-56f9-b4e0-5feeb97692e0</t>
+          <t>29ba93ba-238e-5aad-930a-a621b0f43b5b</t>
         </is>
       </c>
       <c r="E19" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T7 data value</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="38" t="inlineStr">
         <is>
-          <t>ASS_INSTALL_DATE_TXT</t>
+          <t>ASS_FLOW_RATE_TXT</t>
         </is>
       </c>
       <c r="B20" s="38" t="inlineStr">
@@ -4035,24 +4170,24 @@
       </c>
       <c r="C20" s="38" t="inlineStr">
         <is>
-          <t>ASS_MNG</t>
+          <t>HVC_SYSTEMS</t>
         </is>
       </c>
       <c r="D20" s="38" t="inlineStr">
         <is>
-          <t>953575a9-1d0c-5bb5-a4d2-c52b4b4adf96</t>
+          <t>d9a5078f-1c08-56f9-b4e0-5feeb97692e0</t>
         </is>
       </c>
       <c r="E20" s="38" t="inlineStr">
         <is>
-          <t>T7 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="38" t="inlineStr">
         <is>
-          <t>ASS_ITEM_CODE_TXT</t>
+          <t>ASS_INSTALL_DATE_TXT</t>
         </is>
       </c>
       <c r="B21" s="38" t="inlineStr">
@@ -4067,19 +4202,19 @@
       </c>
       <c r="D21" s="38" t="inlineStr">
         <is>
-          <t>d2e3f4a5-b6c7-4d8e-9f0a-1b2c3d4e5f6a</t>
+          <t>953575a9-1d0c-5bb5-a4d2-c52b4b4adf96</t>
         </is>
       </c>
       <c r="E21" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T7 data value</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="38" t="inlineStr">
         <is>
-          <t>ASS_KEYNOTE_TXT</t>
+          <t>ASS_ITEM_CODE_TXT</t>
         </is>
       </c>
       <c r="B22" s="38" t="inlineStr">
@@ -4094,19 +4229,19 @@
       </c>
       <c r="D22" s="38" t="inlineStr">
         <is>
-          <t>a1b2c3d4-501f-4a01-b001-000000000131</t>
+          <t>d2e3f4a5-b6c7-4d8e-9f0a-1b2c3d4e5f6a</t>
         </is>
       </c>
       <c r="E22" s="38" t="inlineStr">
         <is>
-          <t>T4 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="38" t="inlineStr">
         <is>
-          <t>ASS_LVL_COD_TXT</t>
+          <t>ASS_KEYNOTE_TXT</t>
         </is>
       </c>
       <c r="B23" s="38" t="inlineStr">
@@ -4121,19 +4256,19 @@
       </c>
       <c r="D23" s="38" t="inlineStr">
         <is>
-          <t>b1e51fab-fa88-50df-8b2f-bcdbe48e7c78</t>
+          <t>a1b2c3d4-501f-4a01-b001-000000000131</t>
         </is>
       </c>
       <c r="E23" s="38" t="inlineStr">
         <is>
-          <t>T8 data value</t>
+          <t>T4 data value</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="38" t="inlineStr">
         <is>
-          <t>ASS_MANUFACTURER_TXT</t>
+          <t>ASS_LVL_COD_TXT</t>
         </is>
       </c>
       <c r="B24" s="38" t="inlineStr">
@@ -4148,19 +4283,19 @@
       </c>
       <c r="D24" s="38" t="inlineStr">
         <is>
-          <t>822bb665-a508-5268-b490-28d8546d6300</t>
+          <t>b1e51fab-fa88-50df-8b2f-bcdbe48e7c78</t>
         </is>
       </c>
       <c r="E24" s="38" t="inlineStr">
         <is>
-          <t>T6 data value</t>
+          <t>T8 data value</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>ASS_MODEL_NR_TXT</t>
+          <t>ASS_MANUFACTURER_TXT</t>
         </is>
       </c>
       <c r="B25" s="38" t="inlineStr">
@@ -4175,7 +4310,7 @@
       </c>
       <c r="D25" s="38" t="inlineStr">
         <is>
-          <t>305de400-5d2f-54f6-a4ed-acc93f5a1ab2</t>
+          <t>822bb665-a508-5268-b490-28d8546d6300</t>
         </is>
       </c>
       <c r="E25" s="38" t="inlineStr">
@@ -4187,7 +4322,7 @@
     <row r="26">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>ASS_MODEL_REF_TXT</t>
+          <t>ASS_MODEL_NR_TXT</t>
         </is>
       </c>
       <c r="B26" s="38" t="inlineStr">
@@ -4202,19 +4337,19 @@
       </c>
       <c r="D26" s="38" t="inlineStr">
         <is>
-          <t>a1b2c3d4-5011-4a01-b001-000000000117</t>
+          <t>305de400-5d2f-54f6-a4ed-acc93f5a1ab2</t>
         </is>
       </c>
       <c r="E26" s="38" t="inlineStr">
         <is>
-          <t>T4 data value</t>
+          <t>T6 data value</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>ASS_PMT_CERT_DATE_DT</t>
+          <t>ASS_MODEL_REF_TXT</t>
         </is>
       </c>
       <c r="B27" s="38" t="inlineStr">
@@ -4224,24 +4359,24 @@
       </c>
       <c r="C27" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D27" s="38" t="inlineStr">
         <is>
-          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d52</t>
+          <t>a1b2c3d4-5011-4a01-b001-000000000117</t>
         </is>
       </c>
       <c r="E27" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T4 data value</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>ASS_PMT_CERT_NO_NR_DISP_TXT</t>
+          <t>ASS_PMT_CERT_DATE_DT</t>
         </is>
       </c>
       <c r="B28" s="38" t="inlineStr">
@@ -4256,7 +4391,7 @@
       </c>
       <c r="D28" s="38" t="inlineStr">
         <is>
-          <t>1fee3b2b-7f2a-56a5-9d89-81d40113b725</t>
+          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d52</t>
         </is>
       </c>
       <c r="E28" s="38" t="inlineStr">
@@ -4268,7 +4403,7 @@
     <row r="29">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t>ASS_PMT_LAST_VALUED_DT</t>
+          <t>ASS_PMT_CERT_NO_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B29" s="38" t="inlineStr">
@@ -4283,7 +4418,7 @@
       </c>
       <c r="D29" s="38" t="inlineStr">
         <is>
-          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d53</t>
+          <t>1fee3b2b-7f2a-56a5-9d89-81d40113b725</t>
         </is>
       </c>
       <c r="E29" s="38" t="inlineStr">
@@ -4295,7 +4430,7 @@
     <row r="30">
       <c r="A30" s="38" t="inlineStr">
         <is>
-          <t>ASS_PMT_PCT_COMPLETE_NR_DISP_TXT</t>
+          <t>ASS_PMT_LAST_VALUED_DT</t>
         </is>
       </c>
       <c r="B30" s="38" t="inlineStr">
@@ -4310,7 +4445,7 @@
       </c>
       <c r="D30" s="38" t="inlineStr">
         <is>
-          <t>f27e6d2a-a647-5fd5-9c41-9ef2a54f22e3</t>
+          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d53</t>
         </is>
       </c>
       <c r="E30" s="38" t="inlineStr">
@@ -4322,7 +4457,7 @@
     <row r="31">
       <c r="A31" s="38" t="inlineStr">
         <is>
-          <t>ASS_POWER_RATING_TXT</t>
+          <t>ASS_PMT_PCT_COMPLETE_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B31" s="38" t="inlineStr">
@@ -4332,12 +4467,12 @@
       </c>
       <c r="C31" s="38" t="inlineStr">
         <is>
-          <t>ELC_PWR</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D31" s="38" t="inlineStr">
         <is>
-          <t>28c52839-f0b9-55f6-bc9e-7cad2149acc3</t>
+          <t>f27e6d2a-a647-5fd5-9c41-9ef2a54f22e3</t>
         </is>
       </c>
       <c r="E31" s="38" t="inlineStr">
@@ -4349,7 +4484,7 @@
     <row r="32">
       <c r="A32" s="38" t="inlineStr">
         <is>
-          <t>ASS_STATUS_TXT</t>
+          <t>ASS_POWER_RATING_TXT</t>
         </is>
       </c>
       <c r="B32" s="38" t="inlineStr">
@@ -4359,24 +4494,24 @@
       </c>
       <c r="C32" s="38" t="inlineStr">
         <is>
-          <t>ASS_MNG</t>
+          <t>ELC_PWR</t>
         </is>
       </c>
       <c r="D32" s="38" t="inlineStr">
         <is>
-          <t>b97665a8-5e34-585b-9674-fbdd83d7637f</t>
+          <t>28c52839-f0b9-55f6-bc9e-7cad2149acc3</t>
         </is>
       </c>
       <c r="E32" s="38" t="inlineStr">
         <is>
-          <t>T2 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="38" t="inlineStr">
         <is>
-          <t>ASS_SYSTEMS_TXT</t>
+          <t>ASS_QC_INSPECTOR_TXT</t>
         </is>
       </c>
       <c r="B33" s="38" t="inlineStr">
@@ -4391,19 +4526,19 @@
       </c>
       <c r="D33" s="38" t="inlineStr">
         <is>
-          <t>e3f4a5b6-c7d8-4e9f-a0b1-2c3d4e5f6a7b</t>
+          <t>a028f908-b100-53bc-b21a-1a0a6a03ffac</t>
         </is>
       </c>
       <c r="E33" s="38" t="inlineStr">
         <is>
-          <t>T2 data value</t>
+          <t>T7 data value</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="38" t="inlineStr">
         <is>
-          <t>ASS_TAG_1_TXT</t>
+          <t>ASS_SPOOL_NR_TXT</t>
         </is>
       </c>
       <c r="B34" s="38" t="inlineStr">
@@ -4418,19 +4553,19 @@
       </c>
       <c r="D34" s="38" t="inlineStr">
         <is>
-          <t>1eeb577d-342d-5039-97f1-f1dd8d80c8c4</t>
+          <t>1a4353be-eaaa-5e46-95ee-b64a74667194</t>
         </is>
       </c>
       <c r="E34" s="38" t="inlineStr">
         <is>
-          <t>T1 data value</t>
+          <t>T7 data value</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="38" t="inlineStr">
         <is>
-          <t>ASS_TAG_2_TXT</t>
+          <t>ASS_STATUS_TXT</t>
         </is>
       </c>
       <c r="B35" s="38" t="inlineStr">
@@ -4445,7 +4580,7 @@
       </c>
       <c r="D35" s="38" t="inlineStr">
         <is>
-          <t>bf6cb687-478f-459a-8c5d-ece073c24831</t>
+          <t>b97665a8-5e34-585b-9674-fbdd83d7637f</t>
         </is>
       </c>
       <c r="E35" s="38" t="inlineStr">
@@ -4457,7 +4592,7 @@
     <row r="36">
       <c r="A36" s="38" t="inlineStr">
         <is>
-          <t>ASS_TRACE_SEQ_NR_DISP_TXT</t>
+          <t>ASS_SYSTEMS_TXT</t>
         </is>
       </c>
       <c r="B36" s="38" t="inlineStr">
@@ -4472,19 +4607,19 @@
       </c>
       <c r="D36" s="38" t="inlineStr">
         <is>
-          <t>d66a235f-2250-590a-8a9f-b5bd78f330da</t>
+          <t>e3f4a5b6-c7d8-4e9f-a0b1-2c3d4e5f6a7b</t>
         </is>
       </c>
       <c r="E36" s="38" t="inlineStr">
         <is>
-          <t>T10 data value</t>
+          <t>T2 data value</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="38" t="inlineStr">
         <is>
-          <t>ASS_UNICLASS_2015_TXT</t>
+          <t>ASS_TAG_1_TXT</t>
         </is>
       </c>
       <c r="B37" s="38" t="inlineStr">
@@ -4499,19 +4634,19 @@
       </c>
       <c r="D37" s="38" t="inlineStr">
         <is>
-          <t>211dbcbc-361e-513e-a25c-ba0c730c6409</t>
+          <t>1eeb577d-342d-5039-97f1-f1dd8d80c8c4</t>
         </is>
       </c>
       <c r="E37" s="38" t="inlineStr">
         <is>
-          <t>T10 data value</t>
+          <t>T1 data value</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="38" t="inlineStr">
         <is>
-          <t>ASS_VAR_INSTRUCTION_DT</t>
+          <t>ASS_TAG_2_TXT</t>
         </is>
       </c>
       <c r="B38" s="38" t="inlineStr">
@@ -4521,24 +4656,24 @@
       </c>
       <c r="C38" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D38" s="38" t="inlineStr">
         <is>
-          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d61</t>
+          <t>bf6cb687-478f-459a-8c5d-ece073c24831</t>
         </is>
       </c>
       <c r="E38" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T2 data value</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="38" t="inlineStr">
         <is>
-          <t>ASS_VAR_NO_TXT</t>
+          <t>ASS_TRACE_SEQ_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B39" s="38" t="inlineStr">
@@ -4548,24 +4683,24 @@
       </c>
       <c r="C39" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D39" s="38" t="inlineStr">
         <is>
-          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d60</t>
+          <t>d66a235f-2250-590a-8a9f-b5bd78f330da</t>
         </is>
       </c>
       <c r="E39" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T10 data value</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="38" t="inlineStr">
         <is>
-          <t>ASS_VAR_VALUATION_NR_DISP_TXT</t>
+          <t>ASS_UNICLASS_2015_TXT</t>
         </is>
       </c>
       <c r="B40" s="38" t="inlineStr">
@@ -4575,24 +4710,24 @@
       </c>
       <c r="C40" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D40" s="38" t="inlineStr">
         <is>
-          <t>8854c07f-d664-545c-a5a3-89c0be61961a</t>
+          <t>211dbcbc-361e-513e-a25c-ba0c730c6409</t>
         </is>
       </c>
       <c r="E40" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T10 data value</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="38" t="inlineStr">
         <is>
-          <t>ASS_WARRANTY_LABOR_TXT</t>
+          <t>ASS_VAR_INSTRUCTION_DT</t>
         </is>
       </c>
       <c r="B41" s="38" t="inlineStr">
@@ -4602,24 +4737,24 @@
       </c>
       <c r="C41" s="38" t="inlineStr">
         <is>
-          <t>ASS_MNG</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D41" s="38" t="inlineStr">
         <is>
-          <t>185175fb-822c-5978-9955-1ffd1fa2025c</t>
+          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d61</t>
         </is>
       </c>
       <c r="E41" s="38" t="inlineStr">
         <is>
-          <t>T9 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="38" t="inlineStr">
         <is>
-          <t>ASS_WARRANTY_PARTS_TXT</t>
+          <t>ASS_VAR_NO_TXT</t>
         </is>
       </c>
       <c r="B42" s="38" t="inlineStr">
@@ -4629,24 +4764,24 @@
       </c>
       <c r="C42" s="38" t="inlineStr">
         <is>
-          <t>ASS_MNG</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D42" s="38" t="inlineStr">
         <is>
-          <t>400e0672-13f4-5383-aa9d-9f276864d677</t>
+          <t>b9d4e1a2-7c63-4f89-9e0a-1f5a2c8b3d60</t>
         </is>
       </c>
       <c r="E42" s="38" t="inlineStr">
         <is>
-          <t>T9 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t>ASS_WARRANTY_TXT</t>
+          <t>ASS_VAR_VALUATION_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B43" s="38" t="inlineStr">
@@ -4656,24 +4791,24 @@
       </c>
       <c r="C43" s="38" t="inlineStr">
         <is>
-          <t>ASS_MNG</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D43" s="38" t="inlineStr">
         <is>
-          <t>b3c4d5e6-f7a8-4b9c-0d1e-2f3a4b5c6d7a</t>
+          <t>8854c07f-d664-545c-a5a3-89c0be61961a</t>
         </is>
       </c>
       <c r="E43" s="38" t="inlineStr">
         <is>
-          <t>T9 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="38" t="inlineStr">
         <is>
-          <t>ASS_ZONE_TXT</t>
+          <t>ASS_WARRANTY_LABOR_TXT</t>
         </is>
       </c>
       <c r="B44" s="38" t="inlineStr">
@@ -4688,19 +4823,19 @@
       </c>
       <c r="D44" s="38" t="inlineStr">
         <is>
-          <t>dc0d940f-e4ce-5e73-a0a7-fc7094148c84</t>
+          <t>185175fb-822c-5978-9955-1ffd1fa2025c</t>
         </is>
       </c>
       <c r="E44" s="38" t="inlineStr">
         <is>
-          <t>T8 data value</t>
+          <t>T9 data value</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="38" t="inlineStr">
         <is>
-          <t>CBN_A1_A3_KG_CO2E_DISP_TXT</t>
+          <t>ASS_WARRANTY_PARTS_TXT</t>
         </is>
       </c>
       <c r="B45" s="38" t="inlineStr">
@@ -4710,24 +4845,24 @@
       </c>
       <c r="C45" s="38" t="inlineStr">
         <is>
-          <t>PER_SUST</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D45" s="38" t="inlineStr">
         <is>
-          <t>e72731ee-88d0-5341-b458-4ce288e5fbe4</t>
+          <t>400e0672-13f4-5383-aa9d-9f276864d677</t>
         </is>
       </c>
       <c r="E45" s="38" t="inlineStr">
         <is>
-          <t>T6 data value</t>
+          <t>T9 data value</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t>CBN_A4_KG_CO2E_DISP_TXT</t>
+          <t>ASS_WARRANTY_TXT</t>
         </is>
       </c>
       <c r="B46" s="38" t="inlineStr">
@@ -4737,24 +4872,24 @@
       </c>
       <c r="C46" s="38" t="inlineStr">
         <is>
-          <t>PER_SUST</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D46" s="38" t="inlineStr">
         <is>
-          <t>434c64bc-c14b-5c9e-8378-dece87752dca</t>
+          <t>b3c4d5e6-f7a8-4b9c-0d1e-2f3a4b5c6d7a</t>
         </is>
       </c>
       <c r="E46" s="38" t="inlineStr">
         <is>
-          <t>T6 data value</t>
+          <t>T9 data value</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="38" t="inlineStr">
         <is>
-          <t>CBN_B6_KG_CO2E_YR_DISP_TXT</t>
+          <t>ASS_ZONE_TXT</t>
         </is>
       </c>
       <c r="B47" s="38" t="inlineStr">
@@ -4764,24 +4899,24 @@
       </c>
       <c r="C47" s="38" t="inlineStr">
         <is>
-          <t>PER_SUST</t>
+          <t>ASS_MNG</t>
         </is>
       </c>
       <c r="D47" s="38" t="inlineStr">
         <is>
-          <t>d45fbd40-963e-5e52-864f-e4964ef3b449</t>
+          <t>dc0d940f-e4ce-5e73-a0a7-fc7094148c84</t>
         </is>
       </c>
       <c r="E47" s="38" t="inlineStr">
         <is>
-          <t>T6 data value</t>
+          <t>T8 data value</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t>CLASH_RESOLUTION_STATUS_TXT</t>
+          <t>CBN_A1_A3_KG_CO2E_DISP_TXT</t>
         </is>
       </c>
       <c r="B48" s="38" t="inlineStr">
@@ -4791,24 +4926,24 @@
       </c>
       <c r="C48" s="38" t="inlineStr">
         <is>
-          <t>CLASH_COORDINATION</t>
+          <t>PER_SUST</t>
         </is>
       </c>
       <c r="D48" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-0008-4000-8000-000000000003</t>
+          <t>e72731ee-88d0-5341-b458-4ce288e5fbe4</t>
         </is>
       </c>
       <c r="E48" s="38" t="inlineStr">
         <is>
-          <t>T8 data value</t>
+          <t>T6 data value</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>CLASH_TRIAGE_CATEGORY_TXT</t>
+          <t>CBN_A4_KG_CO2E_DISP_TXT</t>
         </is>
       </c>
       <c r="B49" s="38" t="inlineStr">
@@ -4818,24 +4953,24 @@
       </c>
       <c r="C49" s="38" t="inlineStr">
         <is>
-          <t>CLASH_COORDINATION</t>
+          <t>PER_SUST</t>
         </is>
       </c>
       <c r="D49" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-0008-4000-8000-000000000002</t>
+          <t>434c64bc-c14b-5c9e-8378-dece87752dca</t>
         </is>
       </c>
       <c r="E49" s="38" t="inlineStr">
         <is>
-          <t>T8 data value</t>
+          <t>T6 data value</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="38" t="inlineStr">
         <is>
-          <t>CLASH_TRIAGE_SEVERITY_NR_DISP_TXT</t>
+          <t>CBN_B6_KG_CO2E_YR_DISP_TXT</t>
         </is>
       </c>
       <c r="B50" s="38" t="inlineStr">
@@ -4845,24 +4980,24 @@
       </c>
       <c r="C50" s="38" t="inlineStr">
         <is>
-          <t>CLASH_COORDINATION</t>
+          <t>PER_SUST</t>
         </is>
       </c>
       <c r="D50" s="38" t="inlineStr">
         <is>
-          <t>24b29d51-28da-59b4-a011-007d932651b7</t>
+          <t>d45fbd40-963e-5e52-864f-e4964ef3b449</t>
         </is>
       </c>
       <c r="E50" s="38" t="inlineStr">
         <is>
-          <t>T8 data value</t>
+          <t>T6 data value</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t>COMM_DATE_TXT</t>
+          <t>CLASH_RESOLUTION_STATUS_TXT</t>
         </is>
       </c>
       <c r="B51" s="38" t="inlineStr">
@@ -4872,24 +5007,24 @@
       </c>
       <c r="C51" s="38" t="inlineStr">
         <is>
-          <t>COMMISSIONING</t>
+          <t>CLASH_COORDINATION</t>
         </is>
       </c>
       <c r="D51" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-0004-4000-8000-000000000002</t>
+          <t>5753b5aa-0008-4000-8000-000000000003</t>
         </is>
       </c>
       <c r="E51" s="38" t="inlineStr">
         <is>
-          <t>T4 data value</t>
+          <t>T8 data value</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t>COMM_OPERATIVE_TXT</t>
+          <t>CLASH_TRIAGE_CATEGORY_TXT</t>
         </is>
       </c>
       <c r="B52" s="38" t="inlineStr">
@@ -4899,24 +5034,24 @@
       </c>
       <c r="C52" s="38" t="inlineStr">
         <is>
-          <t>COMMISSIONING</t>
+          <t>CLASH_COORDINATION</t>
         </is>
       </c>
       <c r="D52" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-0004-4000-8000-000000000003</t>
+          <t>5753b5aa-0008-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="E52" s="38" t="inlineStr">
         <is>
-          <t>T4 data value</t>
+          <t>T8 data value</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="38" t="inlineStr">
         <is>
-          <t>COMM_STATE_TXT</t>
+          <t>CLASH_TRIAGE_SEVERITY_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B53" s="38" t="inlineStr">
@@ -4926,24 +5061,24 @@
       </c>
       <c r="C53" s="38" t="inlineStr">
         <is>
-          <t>COMMISSIONING</t>
+          <t>CLASH_COORDINATION</t>
         </is>
       </c>
       <c r="D53" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-0004-4000-8000-000000000001</t>
+          <t>24b29d51-28da-59b4-a011-007d932651b7</t>
         </is>
       </c>
       <c r="E53" s="38" t="inlineStr">
         <is>
-          <t>T4 data value</t>
+          <t>T8 data value</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="38" t="inlineStr">
         <is>
-          <t>CST_INSTALL_HRS_DISP_TXT</t>
+          <t>COMM_DATE_TXT</t>
         </is>
       </c>
       <c r="B54" s="38" t="inlineStr">
@@ -4953,24 +5088,24 @@
       </c>
       <c r="C54" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>COMMISSIONING</t>
         </is>
       </c>
       <c r="D54" s="38" t="inlineStr">
         <is>
-          <t>84726a5b-ca7f-59a8-9d3b-7d9f5b8fe4f3</t>
+          <t>5753b5aa-0004-4000-8000-000000000002</t>
         </is>
       </c>
       <c r="E54" s="38" t="inlineStr">
         <is>
-          <t>T7 data value</t>
+          <t>T4 data value</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="38" t="inlineStr">
         <is>
-          <t>CST_INTL_PRICE_USD_DISP_TXT</t>
+          <t>COMM_OPERATIVE_TXT</t>
         </is>
       </c>
       <c r="B55" s="38" t="inlineStr">
@@ -4980,24 +5115,24 @@
       </c>
       <c r="C55" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>COMMISSIONING</t>
         </is>
       </c>
       <c r="D55" s="38" t="inlineStr">
         <is>
-          <t>e1c19fcb-f0bf-552a-a795-9e28918bb81b</t>
+          <t>5753b5aa-0004-4000-8000-000000000003</t>
         </is>
       </c>
       <c r="E55" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T4 data value</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="38" t="inlineStr">
         <is>
-          <t>CST_QUOTE_REF_TXT</t>
+          <t>COMM_STATE_TXT</t>
         </is>
       </c>
       <c r="B56" s="38" t="inlineStr">
@@ -5007,24 +5142,24 @@
       </c>
       <c r="C56" s="38" t="inlineStr">
         <is>
-          <t>CST_PROC</t>
+          <t>COMMISSIONING</t>
         </is>
       </c>
       <c r="D56" s="38" t="inlineStr">
         <is>
-          <t>4de58d8f-38e2-584f-b8aa-5a5744a80fcd</t>
+          <t>5753b5aa-0004-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="E56" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T4 data value</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="38" t="inlineStr">
         <is>
-          <t>CST_UG_PRICE_UGX_DISP_TXT</t>
+          <t>CST_INSTALL_HRS_DISP_TXT</t>
         </is>
       </c>
       <c r="B57" s="38" t="inlineStr">
@@ -5039,19 +5174,19 @@
       </c>
       <c r="D57" s="38" t="inlineStr">
         <is>
-          <t>1a55a7cb-fa8e-51bf-944b-e173d9026299</t>
+          <t>84726a5b-ca7f-59a8-9d3b-7d9f5b8fe4f3</t>
         </is>
       </c>
       <c r="E57" s="38" t="inlineStr">
         <is>
-          <t>T5 data value</t>
+          <t>T7 data value</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="38" t="inlineStr">
         <is>
-          <t>HEALTH_SCORE_LAST_NR_DISP_TXT</t>
+          <t>CST_INTL_PRICE_USD_DISP_TXT</t>
         </is>
       </c>
       <c r="B58" s="38" t="inlineStr">
@@ -5061,24 +5196,24 @@
       </c>
       <c r="C58" s="38" t="inlineStr">
         <is>
-          <t>HEALTH_METRICS</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D58" s="38" t="inlineStr">
         <is>
-          <t>7c4f149b-46cf-50d7-9c10-8fbd2bdd80f8</t>
+          <t>e1c19fcb-f0bf-552a-a795-9e28918bb81b</t>
         </is>
       </c>
       <c r="E58" s="38" t="inlineStr">
         <is>
-          <t>T9 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="38" t="inlineStr">
         <is>
-          <t>IFC_PSET_OVERRIDE_TXT</t>
+          <t>CST_QUOTE_REF_TXT</t>
         </is>
       </c>
       <c r="B59" s="38" t="inlineStr">
@@ -5088,24 +5223,24 @@
       </c>
       <c r="C59" s="38" t="inlineStr">
         <is>
-          <t>IFC_EXCH</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D59" s="38" t="inlineStr">
         <is>
-          <t>5753b5aa-000a-4000-8000-000000000001</t>
+          <t>4de58d8f-38e2-584f-b8aa-5a5744a80fcd</t>
         </is>
       </c>
       <c r="E59" s="38" t="inlineStr">
         <is>
-          <t>T10 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="38" t="inlineStr">
         <is>
-          <t>MEC_SYS_TXT</t>
+          <t>CST_UG_PRICE_UGX_DISP_TXT</t>
         </is>
       </c>
       <c r="B60" s="38" t="inlineStr">
@@ -5115,24 +5250,24 @@
       </c>
       <c r="C60" s="38" t="inlineStr">
         <is>
-          <t>HVC_SYSTEMS</t>
+          <t>CST_PROC</t>
         </is>
       </c>
       <c r="D60" s="38" t="inlineStr">
         <is>
-          <t>b8c9d0e1-f2a3-4b4c-d5e6-f7a8b9c0d1e2</t>
+          <t>1a55a7cb-fa8e-51bf-944b-e173d9026299</t>
         </is>
       </c>
       <c r="E60" s="38" t="inlineStr">
         <is>
-          <t>T2 data value</t>
+          <t>T5 data value</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="38" t="inlineStr">
         <is>
-          <t>RGL_STD_TXT</t>
+          <t>HEALTH_SCORE_LAST_NR_DISP_TXT</t>
         </is>
       </c>
       <c r="B61" s="38" t="inlineStr">
@@ -5142,110 +5277,110 @@
       </c>
       <c r="C61" s="38" t="inlineStr">
         <is>
-          <t>RGL_CMPL</t>
+          <t>HEALTH_METRICS</t>
         </is>
       </c>
       <c r="D61" s="38" t="inlineStr">
         <is>
-          <t>19d2a36a-8e02-57f9-8b00-66b7c0a151cf</t>
+          <t>7c4f149b-46cf-50d7-9c10-8fbd2bdd80f8</t>
         </is>
       </c>
       <c r="E61" s="38" t="inlineStr">
         <is>
-          <t>T2 data value</t>
+          <t>T9 data value</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="38" t="inlineStr">
         <is>
-          <t>STING_GATE_DATA_STATUS_INT</t>
+          <t>IFC_PSET_OVERRIDE_TXT</t>
         </is>
       </c>
       <c r="B62" s="38" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C62" s="38" t="inlineStr">
         <is>
-          <t>STINGTags_ISO19650</t>
+          <t>IFC_EXCH</t>
         </is>
       </c>
       <c r="D62" s="38" t="inlineStr">
         <is>
-          <t>b7f3e2a1-0002-4a01-b001-0000000a0001</t>
+          <t>5753b5aa-000a-4000-8000-000000000001</t>
         </is>
       </c>
       <c r="E62" s="38" t="inlineStr">
         <is>
-          <t>badge — data gate (plugin-stamped)</t>
+          <t>T10 data value</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="38" t="inlineStr">
         <is>
-          <t>STING_GATE_QA_STATUS_INT</t>
+          <t>MEC_SYS_TXT</t>
         </is>
       </c>
       <c r="B63" s="38" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C63" s="38" t="inlineStr">
         <is>
-          <t>STINGTags_ISO19650</t>
+          <t>HVC_SYSTEMS</t>
         </is>
       </c>
       <c r="D63" s="38" t="inlineStr">
         <is>
-          <t>b7f3e2a1-0002-4a01-b001-0000000a0002</t>
+          <t>b8c9d0e1-f2a3-4b4c-d5e6-f7a8b9c0d1e2</t>
         </is>
       </c>
       <c r="E63" s="38" t="inlineStr">
         <is>
-          <t>badge — QA gate (plugin-stamped)</t>
+          <t>T2 data value</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_10_BOOL</t>
+          <t>RGL_STD_TXT</t>
         </is>
       </c>
       <c r="B64" s="38" t="inlineStr">
         <is>
-          <t>YESNO</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="C64" s="38" t="inlineStr">
         <is>
-          <t>STINGTags_ISO19650</t>
+          <t>RGL_CMPL</t>
         </is>
       </c>
       <c r="D64" s="38" t="inlineStr">
         <is>
-          <t>8be3ef27-42ab-5668-8cd0-a376578c805a</t>
+          <t>19d2a36a-8e02-57f9-8b00-66b7c0a151cf</t>
         </is>
       </c>
       <c r="E64" s="38" t="inlineStr">
         <is>
-          <t>tier gate (if-condition)</t>
+          <t>T2 data value</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_2_BOOL</t>
+          <t>STING_GATE_DATA_STATUS_INT</t>
         </is>
       </c>
       <c r="B65" s="38" t="inlineStr">
         <is>
-          <t>YESNO</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C65" s="38" t="inlineStr">
@@ -5255,24 +5390,24 @@
       </c>
       <c r="D65" s="38" t="inlineStr">
         <is>
-          <t>b1080057-9890-5a0c-959a-46fb8847c766</t>
+          <t>b7f3e2a1-0002-4a01-b001-0000000a0001</t>
         </is>
       </c>
       <c r="E65" s="38" t="inlineStr">
         <is>
-          <t>tier gate (if-condition)</t>
+          <t>badge — data gate (plugin-stamped)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_4_BOOL</t>
+          <t>STING_GATE_QA_STATUS_INT</t>
         </is>
       </c>
       <c r="B66" s="38" t="inlineStr">
         <is>
-          <t>YESNO</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C66" s="38" t="inlineStr">
@@ -5282,19 +5417,19 @@
       </c>
       <c r="D66" s="38" t="inlineStr">
         <is>
-          <t>3ac69694-7584-5ba2-9bce-4d045ca21088</t>
+          <t>b7f3e2a1-0002-4a01-b001-0000000a0002</t>
         </is>
       </c>
       <c r="E66" s="38" t="inlineStr">
         <is>
-          <t>tier gate (if-condition)</t>
+          <t>badge — QA gate (plugin-stamped)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_5_BOOL</t>
+          <t>TAG_PARA_STATE_10_BOOL</t>
         </is>
       </c>
       <c r="B67" s="38" t="inlineStr">
@@ -5309,7 +5444,7 @@
       </c>
       <c r="D67" s="38" t="inlineStr">
         <is>
-          <t>c9045501-eee6-54ce-b725-3ea589ee8025</t>
+          <t>8be3ef27-42ab-5668-8cd0-a376578c805a</t>
         </is>
       </c>
       <c r="E67" s="38" t="inlineStr">
@@ -5321,7 +5456,7 @@
     <row r="68">
       <c r="A68" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_6_BOOL</t>
+          <t>TAG_PARA_STATE_2_BOOL</t>
         </is>
       </c>
       <c r="B68" s="38" t="inlineStr">
@@ -5336,7 +5471,7 @@
       </c>
       <c r="D68" s="38" t="inlineStr">
         <is>
-          <t>9b913556-ac00-5a04-b53c-1e262498ad1d</t>
+          <t>b1080057-9890-5a0c-959a-46fb8847c766</t>
         </is>
       </c>
       <c r="E68" s="38" t="inlineStr">
@@ -5348,7 +5483,7 @@
     <row r="69">
       <c r="A69" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_7_BOOL</t>
+          <t>TAG_PARA_STATE_4_BOOL</t>
         </is>
       </c>
       <c r="B69" s="38" t="inlineStr">
@@ -5363,7 +5498,7 @@
       </c>
       <c r="D69" s="38" t="inlineStr">
         <is>
-          <t>8eb03b28-aaf9-5803-8e87-f0655afbf08d</t>
+          <t>3ac69694-7584-5ba2-9bce-4d045ca21088</t>
         </is>
       </c>
       <c r="E69" s="38" t="inlineStr">
@@ -5375,7 +5510,7 @@
     <row r="70">
       <c r="A70" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_8_BOOL</t>
+          <t>TAG_PARA_STATE_5_BOOL</t>
         </is>
       </c>
       <c r="B70" s="38" t="inlineStr">
@@ -5390,7 +5525,7 @@
       </c>
       <c r="D70" s="38" t="inlineStr">
         <is>
-          <t>dd2f491c-8806-5cd2-bb21-d3b915646070</t>
+          <t>c9045501-eee6-54ce-b725-3ea589ee8025</t>
         </is>
       </c>
       <c r="E70" s="38" t="inlineStr">
@@ -5402,7 +5537,7 @@
     <row r="71">
       <c r="A71" s="38" t="inlineStr">
         <is>
-          <t>TAG_PARA_STATE_9_BOOL</t>
+          <t>TAG_PARA_STATE_6_BOOL</t>
         </is>
       </c>
       <c r="B71" s="38" t="inlineStr">
@@ -5417,7 +5552,7 @@
       </c>
       <c r="D71" s="38" t="inlineStr">
         <is>
-          <t>482475c4-be76-5db3-87a6-8aac4a53dc74</t>
+          <t>9b913556-ac00-5a04-b53c-1e262498ad1d</t>
         </is>
       </c>
       <c r="E71" s="38" t="inlineStr">
@@ -5429,25 +5564,106 @@
     <row r="72">
       <c r="A72" s="38" t="inlineStr">
         <is>
+          <t>TAG_PARA_STATE_7_BOOL</t>
+        </is>
+      </c>
+      <c r="B72" s="38" t="inlineStr">
+        <is>
+          <t>YESNO</t>
+        </is>
+      </c>
+      <c r="C72" s="38" t="inlineStr">
+        <is>
+          <t>STINGTags_ISO19650</t>
+        </is>
+      </c>
+      <c r="D72" s="38" t="inlineStr">
+        <is>
+          <t>8eb03b28-aaf9-5803-8e87-f0655afbf08d</t>
+        </is>
+      </c>
+      <c r="E72" s="38" t="inlineStr">
+        <is>
+          <t>tier gate (if-condition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="38" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_8_BOOL</t>
+        </is>
+      </c>
+      <c r="B73" s="38" t="inlineStr">
+        <is>
+          <t>YESNO</t>
+        </is>
+      </c>
+      <c r="C73" s="38" t="inlineStr">
+        <is>
+          <t>STINGTags_ISO19650</t>
+        </is>
+      </c>
+      <c r="D73" s="38" t="inlineStr">
+        <is>
+          <t>dd2f491c-8806-5cd2-bb21-d3b915646070</t>
+        </is>
+      </c>
+      <c r="E73" s="38" t="inlineStr">
+        <is>
+          <t>tier gate (if-condition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="38" t="inlineStr">
+        <is>
+          <t>TAG_PARA_STATE_9_BOOL</t>
+        </is>
+      </c>
+      <c r="B74" s="38" t="inlineStr">
+        <is>
+          <t>YESNO</t>
+        </is>
+      </c>
+      <c r="C74" s="38" t="inlineStr">
+        <is>
+          <t>STINGTags_ISO19650</t>
+        </is>
+      </c>
+      <c r="D74" s="38" t="inlineStr">
+        <is>
+          <t>482475c4-be76-5db3-87a6-8aac4a53dc74</t>
+        </is>
+      </c>
+      <c r="E74" s="38" t="inlineStr">
+        <is>
+          <t>tier gate (if-condition)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="38" t="inlineStr">
+        <is>
           <t>TAG_WARN_VISIBLE_BOOL</t>
         </is>
       </c>
-      <c r="B72" s="38" t="inlineStr">
+      <c r="B75" s="38" t="inlineStr">
         <is>
           <t>YESNO</t>
         </is>
       </c>
-      <c r="C72" s="38" t="inlineStr">
+      <c r="C75" s="38" t="inlineStr">
         <is>
           <t>STINGTags_ISO19650</t>
         </is>
       </c>
-      <c r="D72" s="38" t="inlineStr">
+      <c r="D75" s="38" t="inlineStr">
         <is>
           <t>11d1c84f-a3f8-5cb9-a4aa-cfe44ef42a8f</t>
         </is>
       </c>
-      <c r="E72" s="38" t="inlineStr">
+      <c r="E75" s="38" t="inlineStr">
         <is>
           <t>badge master on/off</t>
         </is>
